--- a/WorkBot/refactor-experimental/data/orders/Hillcrest Dairy/Hillcrest Dairy_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Hillcrest Dairy/Hillcrest Dairy_Triphammer_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Milk - 2%</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>16.08</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>273.36</t>
-        </is>
+      <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>273.36</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Milk - 2% (12/16oz)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>15.00</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E3" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Milk - Chocolate (12/16oz)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>16.20</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>81.00</t>
-        </is>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>81</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Milk - Chocolate (9/32oz)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>16.65</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>33.30</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="E5" t="n">
+        <v>33.3</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Milk - Skim</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>15.56</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="E6" t="n">
+        <v>15.56</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Milk - Whole</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>16.08</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>48.24</t>
-        </is>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>48.24</v>
       </c>
     </row>
   </sheetData>
